--- a/ASTquizApp/qBanks/UPS.xlsx
+++ b/ASTquizApp/qBanks/UPS.xlsx
@@ -1,24 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programDo\vs\ASTquizApp\ASTquizApp\qBanks\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF8F006-4CDE-4370-AC92-69432B9A6E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$91</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="279" count="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="279">
   <si>
     <t>Answer</t>
   </si>
@@ -900,36 +905,32 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="9" formatCode="0%"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -973,45 +974,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1023,9 +1014,31 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <sz val="11"/>
@@ -1070,29 +1083,16 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1313,7 +1313,7 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
+            <a:lightRig rig="threePt" dir="t">
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
@@ -1380,29 +1380,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P91"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O91"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" hidden="1" customWidth="1" width="13.7109375" style="0"/>
-    <col min="2" max="2" hidden="1" customWidth="1" width="19.0" style="0"/>
-    <col min="3" max="3" hidden="1" customWidth="1" width="6.7109375" style="0"/>
-    <col min="4" max="4" hidden="1" customWidth="1" width="13.140625" style="0"/>
-    <col min="5" max="5" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="6" max="6" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="7" max="7" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="8" max="8" customWidth="1" width="43.710938" style="0"/>
-    <col min="9" max="9" customWidth="1" width="15.0" style="0"/>
-    <col min="10" max="10" customWidth="1" width="18.425781" style="0"/>
-    <col min="11" max="11" customWidth="1" width="13.425781" style="0"/>
-    <col min="12" max="12" customWidth="1" width="12.285156" style="0"/>
-    <col min="13" max="13" customWidth="1" width="9.855469" style="1"/>
-    <col min="14" max="14" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="15" max="15" hidden="1" customWidth="1" width="18.710938" style="1"/>
-    <col min="257" max="16384" customWidth="0" width="9.0" style="0"/>
+    <col min="1" max="1" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.85546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="256" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="8:8" s="2" ht="15.75" customFormat="1">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
@@ -1449,7 +1449,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="8:8" ht="51.0">
+    <row r="2" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>278</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>277</v>
       </c>
       <c r="C2" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>15</v>
@@ -1466,7 +1466,7 @@
         <v>21</v>
       </c>
       <c r="F2" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>189</v>
@@ -1490,13 +1490,13 @@
         <v>21</v>
       </c>
       <c r="N2" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O2" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="8:8" ht="34.5" customHeight="1">
+    <row r="3" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>278</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>277</v>
       </c>
       <c r="C3" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>15</v>
@@ -1513,7 +1513,7 @@
         <v>55</v>
       </c>
       <c r="F3" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>189</v>
@@ -1537,13 +1537,13 @@
         <v>27</v>
       </c>
       <c r="N3" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O3" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="4" spans="8:8" ht="51.0">
+    <row r="4" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>278</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>277</v>
       </c>
       <c r="C4" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>15</v>
@@ -1560,7 +1560,7 @@
         <v>49</v>
       </c>
       <c r="F4" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>196</v>
@@ -1580,13 +1580,13 @@
         <v>49</v>
       </c>
       <c r="N4" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O4" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="5" spans="8:8" ht="51.0">
+    <row r="5" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>278</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>277</v>
       </c>
       <c r="C5" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>15</v>
@@ -1603,7 +1603,7 @@
         <v>55</v>
       </c>
       <c r="F5" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>196</v>
@@ -1623,13 +1623,13 @@
         <v>49</v>
       </c>
       <c r="N5" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O5" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="6" spans="8:8" ht="51.0">
+    <row r="6" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>278</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>277</v>
       </c>
       <c r="C6" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>15</v>
@@ -1646,7 +1646,7 @@
         <v>21</v>
       </c>
       <c r="F6" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>196</v>
@@ -1666,13 +1666,13 @@
         <v>21</v>
       </c>
       <c r="N6" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O6" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="7" spans="8:8" ht="51.0">
+    <row r="7" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>278</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>277</v>
       </c>
       <c r="C7" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>15</v>
@@ -1689,7 +1689,7 @@
         <v>55</v>
       </c>
       <c r="F7" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>189</v>
@@ -1713,13 +1713,13 @@
         <v>27</v>
       </c>
       <c r="N7" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O7" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="8" spans="8:8" ht="51.0">
+    <row r="8" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>278</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>277</v>
       </c>
       <c r="C8" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>15</v>
@@ -1736,7 +1736,7 @@
         <v>49</v>
       </c>
       <c r="F8" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>189</v>
@@ -1760,13 +1760,13 @@
         <v>27</v>
       </c>
       <c r="N8" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O8" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="9" spans="8:8" ht="51.0">
+    <row r="9" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>278</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>277</v>
       </c>
       <c r="C9" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>15</v>
@@ -1783,7 +1783,7 @@
         <v>55</v>
       </c>
       <c r="F9" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>189</v>
@@ -1807,13 +1807,13 @@
         <v>21</v>
       </c>
       <c r="N9" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O9" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="10" spans="8:8" ht="51.0">
+    <row r="10" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>278</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>277</v>
       </c>
       <c r="C10" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>15</v>
@@ -1830,7 +1830,7 @@
         <v>55</v>
       </c>
       <c r="F10" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>189</v>
@@ -1854,13 +1854,13 @@
         <v>49</v>
       </c>
       <c r="N10" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O10" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="11" spans="8:8" ht="51.0">
+    <row r="11" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>278</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>277</v>
       </c>
       <c r="C11" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>15</v>
@@ -1877,7 +1877,7 @@
         <v>21</v>
       </c>
       <c r="F11" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>189</v>
@@ -1901,13 +1901,13 @@
         <v>55</v>
       </c>
       <c r="N11" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O11" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="12" spans="8:8" ht="51.75">
+    <row r="12" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>278</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>277</v>
       </c>
       <c r="C12" s="5">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>15</v>
@@ -1924,7 +1924,7 @@
         <v>49</v>
       </c>
       <c r="F12" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>189</v>
@@ -1948,13 +1948,13 @@
         <v>21</v>
       </c>
       <c r="N12" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O12" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="8:8" ht="51.0">
+    <row r="13" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>278</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>277</v>
       </c>
       <c r="C13" s="5">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>15</v>
@@ -1971,7 +1971,7 @@
         <v>55</v>
       </c>
       <c r="F13" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>196</v>
@@ -1991,13 +1991,13 @@
         <v>21</v>
       </c>
       <c r="N13" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O13" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="14" spans="8:8" ht="51.0">
+    <row r="14" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>278</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>277</v>
       </c>
       <c r="C14" s="5">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>15</v>
@@ -2014,7 +2014,7 @@
         <v>55</v>
       </c>
       <c r="F14" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>189</v>
@@ -2038,13 +2038,13 @@
         <v>21</v>
       </c>
       <c r="N14" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O14" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="15" spans="8:8" ht="51.0">
+    <row r="15" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>278</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>277</v>
       </c>
       <c r="C15" s="5">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>15</v>
@@ -2061,7 +2061,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>196</v>
@@ -2081,13 +2081,13 @@
         <v>49</v>
       </c>
       <c r="N15" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O15" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="16" spans="8:8" ht="51.0">
+    <row r="16" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>278</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>277</v>
       </c>
       <c r="C16" s="5">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>15</v>
@@ -2104,7 +2104,7 @@
         <v>27</v>
       </c>
       <c r="F16" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>189</v>
@@ -2128,13 +2128,13 @@
         <v>49</v>
       </c>
       <c r="N16" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O16" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="17" spans="8:8" s="8" ht="36.0" customFormat="1" customHeight="1">
+    <row r="17" spans="1:15" s="8" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>278</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>277</v>
       </c>
       <c r="C17" s="5">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>15</v>
@@ -2151,7 +2151,7 @@
         <v>55</v>
       </c>
       <c r="F17" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>189</v>
@@ -2175,13 +2175,13 @@
         <v>27</v>
       </c>
       <c r="N17" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O17" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="18" spans="8:8" s="8" ht="51.75" customFormat="1">
+    <row r="18" spans="1:15" s="8" customFormat="1" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>278</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>277</v>
       </c>
       <c r="C18" s="5">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>15</v>
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="F18" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>189</v>
@@ -2222,13 +2222,13 @@
         <v>27</v>
       </c>
       <c r="N18" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O18" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="19" spans="8:8" s="8" ht="51.75" customFormat="1">
+    <row r="19" spans="1:15" s="8" customFormat="1" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>278</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>277</v>
       </c>
       <c r="C19" s="5">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>15</v>
@@ -2245,7 +2245,7 @@
         <v>21</v>
       </c>
       <c r="F19" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>189</v>
@@ -2269,13 +2269,13 @@
         <v>21</v>
       </c>
       <c r="N19" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O19" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="20" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="20" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>278</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>277</v>
       </c>
       <c r="C20" s="5">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>15</v>
@@ -2292,7 +2292,7 @@
         <v>55</v>
       </c>
       <c r="F20" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>189</v>
@@ -2316,13 +2316,13 @@
         <v>27</v>
       </c>
       <c r="N20" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O20" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="21" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="21" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>278</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>277</v>
       </c>
       <c r="C21" s="5">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>15</v>
@@ -2339,7 +2339,7 @@
         <v>49</v>
       </c>
       <c r="F21" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>189</v>
@@ -2363,13 +2363,13 @@
         <v>21</v>
       </c>
       <c r="N21" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O21" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="22" spans="8:8" s="8" ht="51.75" customFormat="1">
+    <row r="22" spans="1:15" s="8" customFormat="1" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>278</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>277</v>
       </c>
       <c r="C22" s="5">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>15</v>
@@ -2386,7 +2386,7 @@
         <v>27</v>
       </c>
       <c r="F22" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>189</v>
@@ -2410,13 +2410,13 @@
         <v>21</v>
       </c>
       <c r="N22" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O22" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="23" spans="8:8" s="8" ht="24.75" customFormat="1" customHeight="1">
+    <row r="23" spans="1:15" s="8" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>278</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>277</v>
       </c>
       <c r="C23" s="5">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>15</v>
@@ -2433,7 +2433,7 @@
         <v>21</v>
       </c>
       <c r="F23" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>189</v>
@@ -2457,13 +2457,13 @@
         <v>49</v>
       </c>
       <c r="N23" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O23" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="24" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="24" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>278</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>277</v>
       </c>
       <c r="C24" s="5">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>15</v>
@@ -2480,7 +2480,7 @@
         <v>55</v>
       </c>
       <c r="F24" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>189</v>
@@ -2504,13 +2504,13 @@
         <v>27</v>
       </c>
       <c r="N24" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O24" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="25" spans="8:8" s="8" ht="27.75" customFormat="1" customHeight="1">
+    <row r="25" spans="1:15" s="8" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>278</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>277</v>
       </c>
       <c r="C25" s="5">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>15</v>
@@ -2527,7 +2527,7 @@
         <v>49</v>
       </c>
       <c r="F25" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>189</v>
@@ -2551,13 +2551,13 @@
         <v>21</v>
       </c>
       <c r="N25" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O25" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="26" spans="8:8" s="8" ht="51.75" customFormat="1">
+    <row r="26" spans="1:15" s="8" customFormat="1" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>278</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>277</v>
       </c>
       <c r="C26" s="5">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>15</v>
@@ -2574,7 +2574,7 @@
         <v>27</v>
       </c>
       <c r="F26" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>189</v>
@@ -2598,13 +2598,13 @@
         <v>49</v>
       </c>
       <c r="N26" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O26" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="27" spans="8:8" s="8" ht="64.5" customFormat="1">
+    <row r="27" spans="1:15" s="8" customFormat="1" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>278</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>277</v>
       </c>
       <c r="C27" s="5">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>15</v>
@@ -2621,7 +2621,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>189</v>
@@ -2645,13 +2645,13 @@
         <v>49</v>
       </c>
       <c r="N27" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O27" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="28" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="28" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>278</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>277</v>
       </c>
       <c r="C28" s="5">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>15</v>
@@ -2668,7 +2668,7 @@
         <v>55</v>
       </c>
       <c r="F28" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>189</v>
@@ -2692,13 +2692,13 @@
         <v>27</v>
       </c>
       <c r="N28" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O28" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="29" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="29" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>278</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>277</v>
       </c>
       <c r="C29" s="5">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>15</v>
@@ -2715,7 +2715,7 @@
         <v>49</v>
       </c>
       <c r="F29" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>189</v>
@@ -2739,13 +2739,13 @@
         <v>55</v>
       </c>
       <c r="N29" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O29" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="30" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="30" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>278</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>277</v>
       </c>
       <c r="C30" s="5">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>15</v>
@@ -2762,7 +2762,7 @@
         <v>27</v>
       </c>
       <c r="F30" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>189</v>
@@ -2786,13 +2786,13 @@
         <v>27</v>
       </c>
       <c r="N30" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O30" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="31" spans="8:8" s="8" ht="27.75" customFormat="1" customHeight="1">
+    <row r="31" spans="1:15" s="8" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>278</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>277</v>
       </c>
       <c r="C31" s="5">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>15</v>
@@ -2809,7 +2809,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>189</v>
@@ -2833,13 +2833,13 @@
         <v>27</v>
       </c>
       <c r="N31" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O31" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="32" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="32" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>278</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>277</v>
       </c>
       <c r="C32" s="5">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>15</v>
@@ -2856,7 +2856,7 @@
         <v>55</v>
       </c>
       <c r="F32" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>189</v>
@@ -2880,13 +2880,13 @@
         <v>55</v>
       </c>
       <c r="N32" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O32" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="33" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="33" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>278</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>277</v>
       </c>
       <c r="C33" s="5">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>15</v>
@@ -2903,7 +2903,7 @@
         <v>49</v>
       </c>
       <c r="F33" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>189</v>
@@ -2927,13 +2927,13 @@
         <v>49</v>
       </c>
       <c r="N33" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O33" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="34" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="34" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>278</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>277</v>
       </c>
       <c r="C34" s="5">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>15</v>
@@ -2950,7 +2950,7 @@
         <v>27</v>
       </c>
       <c r="F34" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>189</v>
@@ -2974,13 +2974,13 @@
         <v>49</v>
       </c>
       <c r="N34" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O34" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="35" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="35" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>278</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>277</v>
       </c>
       <c r="C35" s="5">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>15</v>
@@ -2997,7 +2997,7 @@
         <v>21</v>
       </c>
       <c r="F35" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>196</v>
@@ -3017,13 +3017,13 @@
         <v>21</v>
       </c>
       <c r="N35" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O35" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="36" spans="8:8" s="8" ht="51.75" customFormat="1">
+    <row r="36" spans="1:15" s="8" customFormat="1" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>278</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>277</v>
       </c>
       <c r="C36" s="5">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>15</v>
@@ -3040,7 +3040,7 @@
         <v>55</v>
       </c>
       <c r="F36" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>189</v>
@@ -3064,13 +3064,13 @@
         <v>49</v>
       </c>
       <c r="N36" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O36" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="37" spans="8:8" s="8" ht="51.75" customFormat="1">
+    <row r="37" spans="1:15" s="8" customFormat="1" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>278</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>277</v>
       </c>
       <c r="C37" s="5">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>15</v>
@@ -3087,7 +3087,7 @@
         <v>49</v>
       </c>
       <c r="F37" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>189</v>
@@ -3111,13 +3111,13 @@
         <v>49</v>
       </c>
       <c r="N37" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O37" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="38" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="38" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>278</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>277</v>
       </c>
       <c r="C38" s="5">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>15</v>
@@ -3134,7 +3134,7 @@
         <v>27</v>
       </c>
       <c r="F38" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>189</v>
@@ -3158,13 +3158,13 @@
         <v>21</v>
       </c>
       <c r="N38" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O38" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="39" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="39" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>278</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>277</v>
       </c>
       <c r="C39" s="5">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>15</v>
@@ -3181,7 +3181,7 @@
         <v>21</v>
       </c>
       <c r="F39" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>189</v>
@@ -3205,13 +3205,13 @@
         <v>49</v>
       </c>
       <c r="N39" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O39" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="40" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="40" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>278</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>277</v>
       </c>
       <c r="C40" s="5">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>15</v>
@@ -3228,7 +3228,7 @@
         <v>49</v>
       </c>
       <c r="F40" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>196</v>
@@ -3248,13 +3248,13 @@
         <v>21</v>
       </c>
       <c r="N40" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O40" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="41" spans="8:8" s="8" ht="64.5" customFormat="1">
+    <row r="41" spans="1:15" s="8" customFormat="1" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>278</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>277</v>
       </c>
       <c r="C41" s="5">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>15</v>
@@ -3271,7 +3271,7 @@
         <v>49</v>
       </c>
       <c r="F41" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>189</v>
@@ -3295,13 +3295,13 @@
         <v>49</v>
       </c>
       <c r="N41" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O41" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="42" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="42" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>278</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>277</v>
       </c>
       <c r="C42" s="5">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>15</v>
@@ -3318,7 +3318,7 @@
         <v>27</v>
       </c>
       <c r="F42" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>189</v>
@@ -3342,13 +3342,13 @@
         <v>21</v>
       </c>
       <c r="N42" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O42" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="43" spans="8:8" s="8" ht="46.55" customFormat="1">
+    <row r="43" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>278</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>277</v>
       </c>
       <c r="C43" s="5">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>15</v>
@@ -3365,7 +3365,7 @@
         <v>21</v>
       </c>
       <c r="F43" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>189</v>
@@ -3389,13 +3389,13 @@
         <v>21</v>
       </c>
       <c r="N43" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O43" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="44" spans="8:8" s="8" ht="51.75" customFormat="1">
+    <row r="44" spans="1:15" s="8" customFormat="1" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>278</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>277</v>
       </c>
       <c r="C44" s="5">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>15</v>
@@ -3412,7 +3412,7 @@
         <v>49</v>
       </c>
       <c r="F44" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>196</v>
@@ -3432,13 +3432,13 @@
         <v>49</v>
       </c>
       <c r="N44" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O44" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="45" spans="8:8" s="8" ht="51.75" customFormat="1">
+    <row r="45" spans="1:15" s="8" customFormat="1" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>278</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>277</v>
       </c>
       <c r="C45" s="5">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>15</v>
@@ -3455,7 +3455,7 @@
         <v>55</v>
       </c>
       <c r="F45" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>196</v>
@@ -3475,13 +3475,13 @@
         <v>21</v>
       </c>
       <c r="N45" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O45" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="46" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="46" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>278</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>277</v>
       </c>
       <c r="C46" s="5">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>15</v>
@@ -3498,7 +3498,7 @@
         <v>27</v>
       </c>
       <c r="F46" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>189</v>
@@ -3522,13 +3522,13 @@
         <v>27</v>
       </c>
       <c r="N46" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O46" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="47" spans="8:8" s="8" ht="51.75" customFormat="1">
+    <row r="47" spans="1:15" s="8" customFormat="1" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>278</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>277</v>
       </c>
       <c r="C47" s="5">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>15</v>
@@ -3545,7 +3545,7 @@
         <v>21</v>
       </c>
       <c r="F47" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>189</v>
@@ -3569,13 +3569,13 @@
         <v>49</v>
       </c>
       <c r="N47" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O47" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="48" spans="8:8" s="8" ht="46.55" customFormat="1">
+    <row r="48" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>278</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>277</v>
       </c>
       <c r="C48" s="5">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>15</v>
@@ -3592,7 +3592,7 @@
         <v>49</v>
       </c>
       <c r="F48" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>189</v>
@@ -3616,13 +3616,13 @@
         <v>27</v>
       </c>
       <c r="N48" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O48" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="49" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="49" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>278</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>277</v>
       </c>
       <c r="C49" s="5">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>15</v>
@@ -3639,7 +3639,7 @@
         <v>55</v>
       </c>
       <c r="F49" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>189</v>
@@ -3663,13 +3663,13 @@
         <v>49</v>
       </c>
       <c r="N49" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O49" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="50" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="50" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>278</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>277</v>
       </c>
       <c r="C50" s="5">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>15</v>
@@ -3686,7 +3686,7 @@
         <v>55</v>
       </c>
       <c r="F50" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>189</v>
@@ -3710,13 +3710,13 @@
         <v>27</v>
       </c>
       <c r="N50" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O50" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="51" spans="8:8" s="8" ht="51.75" customFormat="1">
+    <row r="51" spans="1:15" s="8" customFormat="1" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>278</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>277</v>
       </c>
       <c r="C51" s="5">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>15</v>
@@ -3733,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="F51" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>196</v>
@@ -3753,13 +3753,13 @@
         <v>21</v>
       </c>
       <c r="N51" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O51" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="52" spans="8:8" s="8" ht="51.0" customFormat="1">
+    <row r="52" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>278</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>277</v>
       </c>
       <c r="C52" s="5">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>15</v>
@@ -3776,7 +3776,7 @@
         <v>21</v>
       </c>
       <c r="F52" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>189</v>
@@ -3800,13 +3800,13 @@
         <v>49</v>
       </c>
       <c r="N52" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O52" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="53" spans="8:8" s="8" ht="46.55" customFormat="1">
+    <row r="53" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>278</v>
       </c>
@@ -3814,7 +3814,7 @@
         <v>277</v>
       </c>
       <c r="C53" s="5">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>15</v>
@@ -3823,7 +3823,7 @@
         <v>49</v>
       </c>
       <c r="F53" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>196</v>
@@ -3843,13 +3843,13 @@
         <v>21</v>
       </c>
       <c r="N53" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O53" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="8:8" s="8" ht="46.55" customFormat="1">
+    <row r="54" spans="1:15" s="8" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>278</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>277</v>
       </c>
       <c r="C54" s="5">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>15</v>
@@ -3866,7 +3866,7 @@
         <v>55</v>
       </c>
       <c r="F54" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>196</v>
@@ -3886,13 +3886,13 @@
         <v>49</v>
       </c>
       <c r="N54" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O54" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="55" spans="8:8" ht="51.0">
+    <row r="55" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>278</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>277</v>
       </c>
       <c r="C55" s="5">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>15</v>
@@ -3909,7 +3909,7 @@
         <v>49</v>
       </c>
       <c r="F55" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>189</v>
@@ -3933,13 +3933,13 @@
         <v>21</v>
       </c>
       <c r="N55" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O55" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="56" spans="8:8" ht="77.25">
+    <row r="56" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>278</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>277</v>
       </c>
       <c r="C56" s="5">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>15</v>
@@ -3956,7 +3956,7 @@
         <v>27</v>
       </c>
       <c r="F56" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>189</v>
@@ -3980,13 +3980,13 @@
         <v>49</v>
       </c>
       <c r="N56" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O56" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="57" spans="8:8" ht="51.0">
+    <row r="57" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>278</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>277</v>
       </c>
       <c r="C57" s="5">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>15</v>
@@ -4003,7 +4003,7 @@
         <v>49</v>
       </c>
       <c r="F57" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>189</v>
@@ -4027,13 +4027,13 @@
         <v>21</v>
       </c>
       <c r="N57" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O57" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="58" spans="8:8" ht="51.0">
+    <row r="58" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>278</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>277</v>
       </c>
       <c r="C58" s="5">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>15</v>
@@ -4050,7 +4050,7 @@
         <v>55</v>
       </c>
       <c r="F58" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>189</v>
@@ -4059,28 +4059,28 @@
         <v>166</v>
       </c>
       <c r="I58" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K58" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M58" s="4" t="s">
         <v>55</v>
       </c>
       <c r="N58" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O58" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="59" spans="8:8" ht="46.55">
+    <row r="59" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>278</v>
       </c>
@@ -4088,7 +4088,7 @@
         <v>277</v>
       </c>
       <c r="C59" s="5">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>15</v>
@@ -4097,7 +4097,7 @@
         <v>49</v>
       </c>
       <c r="F59" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>196</v>
@@ -4117,13 +4117,13 @@
         <v>49</v>
       </c>
       <c r="N59" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O59" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="60" spans="8:8" ht="46.55">
+    <row r="60" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>278</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>277</v>
       </c>
       <c r="C60" s="5">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>15</v>
@@ -4140,7 +4140,7 @@
         <v>27</v>
       </c>
       <c r="F60" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>196</v>
@@ -4160,13 +4160,13 @@
         <v>21</v>
       </c>
       <c r="N60" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O60" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="61" spans="8:8" ht="51.0">
+    <row r="61" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>278</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>277</v>
       </c>
       <c r="C61" s="5">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>15</v>
@@ -4183,7 +4183,7 @@
         <v>49</v>
       </c>
       <c r="F61" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>196</v>
@@ -4203,13 +4203,13 @@
         <v>21</v>
       </c>
       <c r="N61" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O61" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="8:8" ht="51.0">
+    <row r="62" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>278</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>277</v>
       </c>
       <c r="C62" s="5">
-        <v>61.0</v>
+        <v>61</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>15</v>
@@ -4226,7 +4226,7 @@
         <v>55</v>
       </c>
       <c r="F62" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>196</v>
@@ -4246,13 +4246,13 @@
         <v>49</v>
       </c>
       <c r="N62" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O62" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="63" spans="8:8" ht="51.75">
+    <row r="63" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>278</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>277</v>
       </c>
       <c r="C63" s="5">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>15</v>
@@ -4269,7 +4269,7 @@
         <v>49</v>
       </c>
       <c r="F63" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>196</v>
@@ -4289,13 +4289,13 @@
         <v>21</v>
       </c>
       <c r="N63" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O63" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="64" spans="8:8" ht="51.75">
+    <row r="64" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>278</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>277</v>
       </c>
       <c r="C64" s="5">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>15</v>
@@ -4312,7 +4312,7 @@
         <v>27</v>
       </c>
       <c r="F64" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>196</v>
@@ -4332,13 +4332,13 @@
         <v>21</v>
       </c>
       <c r="N64" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O64" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="65" spans="8:8" ht="46.55">
+    <row r="65" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>278</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>277</v>
       </c>
       <c r="C65" s="5">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>15</v>
@@ -4355,7 +4355,7 @@
         <v>55</v>
       </c>
       <c r="F65" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>189</v>
@@ -4379,13 +4379,13 @@
         <v>21</v>
       </c>
       <c r="N65" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O65" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="66" spans="8:8" ht="46.55">
+    <row r="66" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>278</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>277</v>
       </c>
       <c r="C66" s="5">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>15</v>
@@ -4402,7 +4402,7 @@
         <v>49</v>
       </c>
       <c r="F66" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>189</v>
@@ -4426,13 +4426,13 @@
         <v>55</v>
       </c>
       <c r="N66" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O66" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="67" spans="8:8" ht="46.55">
+    <row r="67" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>278</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>277</v>
       </c>
       <c r="C67" s="5">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>15</v>
@@ -4449,7 +4449,7 @@
         <v>27</v>
       </c>
       <c r="F67" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>189</v>
@@ -4473,13 +4473,13 @@
         <v>27</v>
       </c>
       <c r="N67" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O67" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="68" spans="8:8" ht="46.55">
+    <row r="68" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>278</v>
       </c>
@@ -4487,7 +4487,7 @@
         <v>277</v>
       </c>
       <c r="C68" s="5">
-        <v>67.0</v>
+        <v>67</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>15</v>
@@ -4496,7 +4496,7 @@
         <v>55</v>
       </c>
       <c r="F68" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G68" s="5" t="s">
         <v>189</v>
@@ -4520,13 +4520,13 @@
         <v>49</v>
       </c>
       <c r="N68" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O68" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="69" spans="8:8" ht="51.75">
+    <row r="69" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>278</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>277</v>
       </c>
       <c r="C69" s="5">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>15</v>
@@ -4543,7 +4543,7 @@
         <v>49</v>
       </c>
       <c r="F69" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>196</v>
@@ -4563,13 +4563,13 @@
         <v>49</v>
       </c>
       <c r="N69" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O69" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="70" spans="8:8" ht="51.75">
+    <row r="70" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>278</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>277</v>
       </c>
       <c r="C70" s="5">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>15</v>
@@ -4586,7 +4586,7 @@
         <v>27</v>
       </c>
       <c r="F70" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>196</v>
@@ -4606,13 +4606,13 @@
         <v>21</v>
       </c>
       <c r="N70" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O70" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="71" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="71" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>278</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>277</v>
       </c>
       <c r="C71" s="5">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="D71" s="14" t="s">
         <v>188</v>
@@ -4629,7 +4629,7 @@
         <v>21</v>
       </c>
       <c r="F71" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G71" s="5" t="s">
         <v>189</v>
@@ -4653,13 +4653,13 @@
         <v>21</v>
       </c>
       <c r="N71" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O71" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="72" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="72" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>278</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>277</v>
       </c>
       <c r="C72" s="5">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="D72" s="14" t="s">
         <v>188</v>
@@ -4676,7 +4676,7 @@
         <v>27</v>
       </c>
       <c r="F72" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>196</v>
@@ -4696,13 +4696,13 @@
         <v>21</v>
       </c>
       <c r="N72" s="14">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O72" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="73" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="73" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>278</v>
       </c>
@@ -4710,7 +4710,7 @@
         <v>277</v>
       </c>
       <c r="C73" s="5">
-        <v>72.0</v>
+        <v>72</v>
       </c>
       <c r="D73" s="14" t="s">
         <v>188</v>
@@ -4719,7 +4719,7 @@
         <v>49</v>
       </c>
       <c r="F73" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>189</v>
@@ -4743,13 +4743,13 @@
         <v>21</v>
       </c>
       <c r="N73" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O73" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="74" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="74" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>278</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>277</v>
       </c>
       <c r="C74" s="5">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="D74" s="14" t="s">
         <v>188</v>
@@ -4766,7 +4766,7 @@
         <v>55</v>
       </c>
       <c r="F74" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>189</v>
@@ -4790,13 +4790,13 @@
         <v>55</v>
       </c>
       <c r="N74" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O74" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="75" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="75" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>278</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>277</v>
       </c>
       <c r="C75" s="5">
-        <v>74.0</v>
+        <v>74</v>
       </c>
       <c r="D75" s="14" t="s">
         <v>188</v>
@@ -4813,7 +4813,7 @@
         <v>21</v>
       </c>
       <c r="F75" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>189</v>
@@ -4837,13 +4837,13 @@
         <v>27</v>
       </c>
       <c r="N75" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O75" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="76" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="76" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>278</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>277</v>
       </c>
       <c r="C76" s="5">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="D76" s="14" t="s">
         <v>188</v>
@@ -4860,7 +4860,7 @@
         <v>49</v>
       </c>
       <c r="F76" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>189</v>
@@ -4884,13 +4884,13 @@
         <v>49</v>
       </c>
       <c r="N76" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O76" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="77" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>278</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>277</v>
       </c>
       <c r="C77" s="5">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="D77" s="14" t="s">
         <v>188</v>
@@ -4907,7 +4907,7 @@
         <v>27</v>
       </c>
       <c r="F77" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>189</v>
@@ -4931,13 +4931,13 @@
         <v>55</v>
       </c>
       <c r="N77" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O77" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="78" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="78" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>278</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>277</v>
       </c>
       <c r="C78" s="5">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="D78" s="14" t="s">
         <v>188</v>
@@ -4954,7 +4954,7 @@
         <v>49</v>
       </c>
       <c r="F78" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>189</v>
@@ -4978,13 +4978,13 @@
         <v>27</v>
       </c>
       <c r="N78" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O78" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="79" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="79" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>278</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>277</v>
       </c>
       <c r="C79" s="5">
-        <v>78.0</v>
+        <v>78</v>
       </c>
       <c r="D79" s="14" t="s">
         <v>188</v>
@@ -5001,7 +5001,7 @@
         <v>55</v>
       </c>
       <c r="F79" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>189</v>
@@ -5025,13 +5025,13 @@
         <v>49</v>
       </c>
       <c r="N79" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O79" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="80" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="80" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>278</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>277</v>
       </c>
       <c r="C80" s="5">
-        <v>79.0</v>
+        <v>79</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>225</v>
@@ -5048,7 +5048,7 @@
         <v>21</v>
       </c>
       <c r="F80" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>189</v>
@@ -5072,13 +5072,13 @@
         <v>49</v>
       </c>
       <c r="N80" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O80" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="81" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="81" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>278</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>277</v>
       </c>
       <c r="C81" s="5">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="D81" s="14" t="s">
         <v>225</v>
@@ -5095,7 +5095,7 @@
         <v>55</v>
       </c>
       <c r="F81" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>189</v>
@@ -5119,13 +5119,13 @@
         <v>55</v>
       </c>
       <c r="N81" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O81" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="82" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="82" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>278</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>277</v>
       </c>
       <c r="C82" s="5">
-        <v>81.0</v>
+        <v>81</v>
       </c>
       <c r="D82" s="14" t="s">
         <v>225</v>
@@ -5142,7 +5142,7 @@
         <v>49</v>
       </c>
       <c r="F82" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>189</v>
@@ -5160,19 +5160,19 @@
         <v>0.9</v>
       </c>
       <c r="L82" s="16">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="14" t="s">
         <v>55</v>
       </c>
       <c r="N82" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O82" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="83" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="83" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>278</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>277</v>
       </c>
       <c r="C83" s="5">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="D83" s="14" t="s">
         <v>225</v>
@@ -5189,7 +5189,7 @@
         <v>55</v>
       </c>
       <c r="F83" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>189</v>
@@ -5213,13 +5213,13 @@
         <v>21</v>
       </c>
       <c r="N83" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O83" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="84" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="84" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>278</v>
       </c>
@@ -5227,7 +5227,7 @@
         <v>277</v>
       </c>
       <c r="C84" s="5">
-        <v>83.0</v>
+        <v>83</v>
       </c>
       <c r="D84" s="14" t="s">
         <v>225</v>
@@ -5236,7 +5236,7 @@
         <v>49</v>
       </c>
       <c r="F84" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G84" s="5" t="s">
         <v>189</v>
@@ -5260,13 +5260,13 @@
         <v>49</v>
       </c>
       <c r="N84" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O84" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="85" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="85" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>278</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>277</v>
       </c>
       <c r="C85" s="5">
-        <v>84.0</v>
+        <v>84</v>
       </c>
       <c r="D85" s="14" t="s">
         <v>225</v>
@@ -5283,7 +5283,7 @@
         <v>27</v>
       </c>
       <c r="F85" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>196</v>
@@ -5303,13 +5303,13 @@
         <v>21</v>
       </c>
       <c r="N85" s="14">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O85" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="86" spans="8:8" s="13" ht="85.5" customFormat="1">
+    <row r="86" spans="1:15" s="13" customFormat="1" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>278</v>
       </c>
@@ -5317,7 +5317,7 @@
         <v>277</v>
       </c>
       <c r="C86" s="5">
-        <v>85.0</v>
+        <v>85</v>
       </c>
       <c r="D86" s="14" t="s">
         <v>225</v>
@@ -5326,7 +5326,7 @@
         <v>55</v>
       </c>
       <c r="F86" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G86" s="5" t="s">
         <v>189</v>
@@ -5350,13 +5350,13 @@
         <v>27</v>
       </c>
       <c r="N86" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O86" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="87" spans="8:8" s="13" ht="85.5" customFormat="1">
+    <row r="87" spans="1:15" s="13" customFormat="1" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>278</v>
       </c>
@@ -5364,7 +5364,7 @@
         <v>277</v>
       </c>
       <c r="C87" s="5">
-        <v>86.0</v>
+        <v>86</v>
       </c>
       <c r="D87" s="14" t="s">
         <v>225</v>
@@ -5373,7 +5373,7 @@
         <v>49</v>
       </c>
       <c r="F87" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G87" s="5" t="s">
         <v>189</v>
@@ -5397,13 +5397,13 @@
         <v>27</v>
       </c>
       <c r="N87" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O87" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="88" spans="8:8" s="13" ht="71.25" customFormat="1">
+    <row r="88" spans="1:15" s="13" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>278</v>
       </c>
@@ -5411,7 +5411,7 @@
         <v>277</v>
       </c>
       <c r="C88" s="5">
-        <v>87.0</v>
+        <v>87</v>
       </c>
       <c r="D88" s="14" t="s">
         <v>256</v>
@@ -5420,7 +5420,7 @@
         <v>27</v>
       </c>
       <c r="F88" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G88" s="5" t="s">
         <v>189</v>
@@ -5444,13 +5444,13 @@
         <v>27</v>
       </c>
       <c r="N88" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O88" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="89" spans="8:8" s="13" ht="57.0" customFormat="1">
+    <row r="89" spans="1:15" s="13" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>278</v>
       </c>
@@ -5458,7 +5458,7 @@
         <v>277</v>
       </c>
       <c r="C89" s="5">
-        <v>88.0</v>
+        <v>88</v>
       </c>
       <c r="D89" s="14" t="s">
         <v>263</v>
@@ -5467,7 +5467,7 @@
         <v>55</v>
       </c>
       <c r="F89" s="14">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G89" s="14" t="s">
         <v>189</v>
@@ -5491,13 +5491,13 @@
         <v>55</v>
       </c>
       <c r="N89" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O89" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="90" spans="8:8" s="13" ht="51.0" customFormat="1">
+    <row r="90" spans="1:15" s="13" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>278</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>277</v>
       </c>
       <c r="C90" s="5">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="D90" s="14" t="s">
         <v>263</v>
@@ -5514,7 +5514,7 @@
         <v>49</v>
       </c>
       <c r="F90" s="14">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G90" s="14" t="s">
         <v>189</v>
@@ -5538,13 +5538,13 @@
         <v>27</v>
       </c>
       <c r="N90" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O90" s="14" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="91" spans="8:8" s="13" ht="85.5" customFormat="1">
+    <row r="91" spans="1:15" s="13" customFormat="1" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>278</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>277</v>
       </c>
       <c r="C91" s="5">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="D91" s="14" t="s">
         <v>263</v>
@@ -5561,7 +5561,7 @@
         <v>21</v>
       </c>
       <c r="F91" s="14">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G91" s="14" t="s">
         <v>189</v>
@@ -5585,7 +5585,7 @@
         <v>27</v>
       </c>
       <c r="N91" s="14">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O91" s="14" t="s">
         <v>195</v>
@@ -5593,31 +5593,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H1">
-    <cfRule type="duplicateValues" priority="5" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="9" dxfId="1"/>
-    <cfRule type="duplicateValues" priority="3" dxfId="2"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="3"/>
-    <cfRule type="duplicateValues" priority="1" dxfId="4"/>
-    <cfRule type="duplicateValues" priority="6" dxfId="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>